--- a/scripts/redshift_table.xlsx
+++ b/scripts/redshift_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_RschArchives\RSCH3_upload\kl_mmt\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159A1610-6782-4509-8DDF-059F94D2B0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0998224D-0301-43D2-B19C-DFF9F292DFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D0472C34-474C-4FE1-B401-AA8D4EBE0D9B}"/>
+    <workbookView xWindow="14865" yWindow="255" windowWidth="13935" windowHeight="14070" xr2:uid="{D0472C34-474C-4FE1-B401-AA8D4EBE0D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="redshift_table" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="86">
   <si>
     <t>Set_C</t>
   </si>
@@ -6042,6 +6042,9 @@
         <v>33</v>
       </c>
       <c r="N30" s="6"/>
+      <c r="O30" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" spans="1:15" ht="27" customHeight="1">
       <c r="A31" s="3">
@@ -6445,6 +6448,9 @@
         <v>34</v>
       </c>
       <c r="N41" s="6"/>
+      <c r="O41" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="42" spans="1:15" ht="27" customHeight="1">
       <c r="A42" s="3">
@@ -7501,7 +7507,7 @@
       </c>
       <c r="N71" s="6"/>
       <c r="O71" s="4" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="27" customHeight="1">
@@ -9056,6 +9062,9 @@
         <v>16</v>
       </c>
       <c r="N113" s="6"/>
+      <c r="O113" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="114" spans="1:15" ht="27" customHeight="1">
       <c r="A114" s="3">

--- a/scripts/redshift_table.xlsx
+++ b/scripts/redshift_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_RschArchives\RSCH3_upload\kl_mmt\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0998224D-0301-43D2-B19C-DFF9F292DFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657DC605-0E18-4102-A8BC-3A1145B4D93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14865" yWindow="255" windowWidth="13935" windowHeight="14070" xr2:uid="{D0472C34-474C-4FE1-B401-AA8D4EBE0D9B}"/>
+    <workbookView xWindow="0" yWindow="228" windowWidth="13764" windowHeight="10236" xr2:uid="{D0472C34-474C-4FE1-B401-AA8D4EBE0D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="redshift_table" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="86">
   <si>
     <t>Set_C</t>
   </si>
@@ -319,10 +319,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Hg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>N2a</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -342,14 +338,17 @@
     <t>O3a,Hb</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>Hb,Hg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="164" formatCode="0.000_);[Red]\(0.000\)"/>
+    <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -369,7 +368,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线 Light"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -969,10 +968,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,7 +1275,7 @@
         <family val="3"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+      <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1295,7 +1294,7 @@
         <family val="3"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+      <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1311,7 +1310,7 @@
         <family val="3"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
+      <numFmt numFmtId="164" formatCode="0.000_);[Red]\(0.000\)"/>
     </dxf>
     <dxf>
       <font>
@@ -4466,8 +4465,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="572689" y="49545874"/>
-              <a:ext cx="8323661" cy="3584575"/>
+              <a:off x="595549" y="49545874"/>
+              <a:ext cx="8657036" cy="3584575"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4486,7 +4485,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="zh-CN" altLang="en-US" sz="1100"/>
+                <a:rPr lang="en-US" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -4920,27 +4919,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B49B4158-5F58-414E-8D74-5AE881EF5472}">
   <dimension ref="A1:O144"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="27" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.765625" defaultRowHeight="27" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.23046875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.23046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.3828125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.61328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.3828125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.765625" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.59765625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="7.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.61328125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="7.61328125" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="67" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="67" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.796875" style="4"/>
+    <col min="19" max="16384" width="8.765625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" customHeight="1">
@@ -5173,7 +5172,7 @@
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="27" customHeight="1">
@@ -5622,7 +5621,7 @@
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="27" customHeight="1">
@@ -5892,7 +5891,7 @@
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="27" customHeight="1">
@@ -6326,6 +6325,9 @@
       <c r="N37" s="6" t="s">
         <v>40</v>
       </c>
+      <c r="O37" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="38" spans="1:15" ht="27" customHeight="1">
       <c r="A38" s="3">
@@ -7126,7 +7128,7 @@
       </c>
       <c r="N60" s="6"/>
       <c r="O60" s="4" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="27" customHeight="1">
@@ -7165,6 +7167,9 @@
         <v>15</v>
       </c>
       <c r="N61" s="6"/>
+      <c r="O61" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="62" spans="1:15" ht="27" customHeight="1">
       <c r="A62" s="3">
@@ -7621,7 +7626,7 @@
       </c>
       <c r="N74" s="6"/>
       <c r="O74" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="27" customHeight="1">
@@ -7763,6 +7768,9 @@
         <v>31</v>
       </c>
       <c r="N79" s="6"/>
+      <c r="O79" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="80" spans="1:15" ht="27" customHeight="1">
       <c r="A80" s="3">
@@ -7852,7 +7860,7 @@
         <v>60</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="27" customHeight="1">
@@ -8249,7 +8257,7 @@
       </c>
       <c r="N92" s="6"/>
       <c r="O92" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="27" customHeight="1">
@@ -8716,6 +8724,9 @@
         <v>31</v>
       </c>
       <c r="N104" s="6"/>
+      <c r="O104" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="105" spans="1:15" ht="27" customHeight="1">
       <c r="A105" s="3">
@@ -8974,7 +8985,7 @@
       </c>
       <c r="N111" s="6"/>
       <c r="O111" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="27" customHeight="1">
@@ -9154,6 +9165,9 @@
         <v>42</v>
       </c>
       <c r="N115" s="6"/>
+      <c r="O115" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="116" spans="1:15" ht="27" customHeight="1">
       <c r="A116" s="3">
@@ -9777,7 +9791,7 @@
       </c>
       <c r="N132" s="6"/>
       <c r="O132" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133" spans="1:15" ht="27" customHeight="1">
@@ -9969,6 +9983,9 @@
         <v>41</v>
       </c>
       <c r="N137" s="6"/>
+      <c r="O137" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="138" spans="1:15" ht="27" customHeight="1">
       <c r="A138" s="3">
@@ -10255,13 +10272,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D437F7E-87B7-432E-A785-238CA37AFE4C}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="8.765625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="1"/>
-    <col min="4" max="4" width="12.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.765625" style="1"/>
+    <col min="4" max="4" width="12.921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.765625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
